--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS18"/>
+  <dimension ref="A1:AU18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,10 +532,17 @@
           <t>damage</t>
         </is>
       </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>damage_type</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>attack_multiplier</t>
+        </is>
+      </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
@@ -605,6 +612,16 @@
       <c r="AR5" t="inlineStr">
         <is>
           <t>所需状态</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>伤害类型:0=法术(吃法伤) 1=物理(吃物伤)</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>攻击倍率:物伤/法伤部分乘以本值,0=按1倍</t>
         </is>
       </c>
     </row>
@@ -742,6 +759,12 @@
         <is>
           <t>100*level</t>
         </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -879,6 +902,12 @@
           <t>100*level</t>
         </is>
       </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1015,6 +1044,12 @@
           <t>1000*level</t>
         </is>
       </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1151,6 +1186,12 @@
           <t>10000*level</t>
         </is>
       </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1287,6 +1328,12 @@
           <t>10000*level</t>
         </is>
       </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1426,6 +1473,12 @@
           <t>100*level</t>
         </is>
       </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1562,6 +1615,12 @@
           <t>1000*level</t>
         </is>
       </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1698,6 +1757,12 @@
           <t>10000*level</t>
         </is>
       </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1834,6 +1899,12 @@
           <t>100*level</t>
         </is>
       </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1964,6 +2035,12 @@
           <t>1000*level</t>
         </is>
       </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2100,6 +2177,12 @@
           <t>10000*level</t>
         </is>
       </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2239,6 +2322,12 @@
           <t>10000*level</t>
         </is>
       </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2377,6 +2466,12 @@
         <is>
           <t>10000*level</t>
         </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -717,7 +717,7 @@
         <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>

--- a/data/Skill.xlsx
+++ b/data/Skill.xlsx
@@ -3146,8 +3146,8 @@
       <c r="AT21" t="n">
         <v>1</v>
       </c>
-      <c r="AU21" t="n">
-        <v>0.85</v>
+      <c r="AU21">
+        <v>0.7</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4796,8 +4796,8 @@
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="n">
-        <v>0.85</v>
+      <c r="AU29">
+        <v>0.75</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
@@ -6277,17 +6277,17 @@
       <c r="BD36" t="n">
         <v>1</v>
       </c>
-      <c r="BE36" t="n">
-        <v>0.03</v>
+      <c r="BE36">
+        <v>0.04</v>
       </c>
       <c r="BF36" t="n">
         <v>0</v>
       </c>
-      <c r="BG36" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>8</v>
+      <c r="BG36">
+        <v>0.3</v>
+      </c>
+      <c r="BH36">
+        <v>2</v>
       </c>
       <c r="BI36" t="n">
         <v>0</v>
@@ -6484,17 +6484,17 @@
       <c r="BD37" t="n">
         <v>3</v>
       </c>
-      <c r="BE37" t="n">
-        <v>0.06</v>
+      <c r="BE37">
+        <v>0.07</v>
       </c>
       <c r="BF37" t="n">
         <v>1</v>
       </c>
-      <c r="BG37" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BH37" t="n">
-        <v>4</v>
+      <c r="BG37">
+        <v>0.18</v>
+      </c>
+      <c r="BH37">
+        <v>1</v>
       </c>
       <c r="BI37" t="n">
         <v>0</v>
@@ -6697,11 +6697,11 @@
       <c r="BF38" t="n">
         <v>2</v>
       </c>
-      <c r="BG38" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>3</v>
+      <c r="BG38">
+        <v>0.2</v>
+      </c>
+      <c r="BH38">
+        <v>1</v>
       </c>
       <c r="BI38" t="n">
         <v>0</v>
@@ -7111,11 +7111,11 @@
       <c r="BF40" t="n">
         <v>3</v>
       </c>
-      <c r="BG40" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>10</v>
+      <c r="BG40">
+        <v>0.55</v>
+      </c>
+      <c r="BH40">
+        <v>3</v>
       </c>
       <c r="BI40" t="n">
         <v>0.3</v>
@@ -8099,8 +8099,8 @@
       <c r="AT45" t="n">
         <v>1</v>
       </c>
-      <c r="AU45" t="n">
-        <v>0.75</v>
+      <c r="AU45">
+        <v>0.6</v>
       </c>
       <c r="AV45" t="n">
         <v>4</v>
